--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123675716</v>
       </c>
       <c r="B4" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123675716</v>
       </c>
       <c r="B4" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130207090</v>
       </c>
       <c r="B8" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130207080</v>
       </c>
       <c r="B9" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>91655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R13" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>91653</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R14" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,45 +2201,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B16" t="n">
-        <v>99165</v>
+        <v>57741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R16" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,50 +2313,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>99167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R17" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130207091</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207090</v>
+        <v>130207080</v>
       </c>
       <c r="B8" t="n">
-        <v>91661</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,19 +1355,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510203</v>
+        <v>510283</v>
       </c>
       <c r="R8" t="n">
-        <v>7207324</v>
+        <v>7207343</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207080</v>
+        <v>130207093</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510283</v>
+        <v>510310</v>
       </c>
       <c r="R9" t="n">
-        <v>7207343</v>
+        <v>7207347</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207093</v>
+        <v>130207090</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,23 +1569,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510310</v>
+        <v>510203</v>
       </c>
       <c r="R10" t="n">
-        <v>7207347</v>
+        <v>7207324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>130207097</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,50 +2201,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>99254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R16" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,45 +2308,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B17" t="n">
-        <v>99167</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R17" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,23 +1355,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R8" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207093</v>
+        <v>130207080</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510310</v>
+        <v>510283</v>
       </c>
       <c r="R9" t="n">
-        <v>7207347</v>
+        <v>7207343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,19 +1565,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B13" t="n">
-        <v>91742</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R13" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>91742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R14" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207090</v>
+        <v>130207080</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,19 +1355,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510203</v>
+        <v>510283</v>
       </c>
       <c r="R8" t="n">
-        <v>7207324</v>
+        <v>7207343</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207080</v>
+        <v>130207093</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510283</v>
+        <v>510310</v>
       </c>
       <c r="R9" t="n">
-        <v>7207343</v>
+        <v>7207347</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207093</v>
+        <v>130207090</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,23 +1569,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510310</v>
+        <v>510203</v>
       </c>
       <c r="R10" t="n">
-        <v>7207347</v>
+        <v>7207324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>91742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R13" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>91742</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R14" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,23 +1355,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R8" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207093</v>
+        <v>130207080</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510310</v>
+        <v>510283</v>
       </c>
       <c r="R9" t="n">
-        <v>7207347</v>
+        <v>7207343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,19 +1565,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B13" t="n">
-        <v>91742</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R13" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>91742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R14" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,45 +2201,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B16" t="n">
-        <v>99254</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R16" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,50 +2313,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>99254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R17" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207090</v>
+        <v>130207080</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,19 +1355,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510203</v>
+        <v>510283</v>
       </c>
       <c r="R8" t="n">
-        <v>7207324</v>
+        <v>7207343</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,23 +1462,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R9" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>91742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R13" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>91742</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R14" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,50 +2201,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>99254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R16" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,45 +2308,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B17" t="n">
-        <v>99254</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R17" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B9" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,19 +1462,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R9" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207093</v>
+        <v>130207090</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,23 +1569,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510310</v>
+        <v>510203</v>
       </c>
       <c r="R10" t="n">
-        <v>7207347</v>
+        <v>7207324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2201,45 +2201,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B16" t="n">
-        <v>99254</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R16" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,50 +2313,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>99254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R17" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130207080</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130207093</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130207090</v>
       </c>
       <c r="B10" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91742</v>
+        <v>91745</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91742</v>
+        <v>91745</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>91742</v>
+        <v>91745</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>99254</v>
+        <v>99257</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130207091</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B8" t="n">
-        <v>91731</v>
+        <v>91777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,23 +1355,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R8" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207093</v>
+        <v>130207080</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510310</v>
+        <v>510283</v>
       </c>
       <c r="R9" t="n">
-        <v>7207347</v>
+        <v>7207343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>91751</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,19 +1565,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91745</v>
+        <v>91771</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91745</v>
+        <v>91771</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>91745</v>
+        <v>91771</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>130207089</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>130207097</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,50 +2201,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>99283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R16" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,45 +2308,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B17" t="n">
-        <v>99257</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R17" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B8" t="n">
-        <v>91777</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,19 +1355,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R8" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1454,7 @@
         <v>130207080</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207093</v>
+        <v>130207090</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>91778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,23 +1569,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510310</v>
+        <v>510203</v>
       </c>
       <c r="R10" t="n">
-        <v>7207347</v>
+        <v>7207324</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2201,45 +2201,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B16" t="n">
-        <v>99283</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R16" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,50 +2313,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>99284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R17" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207093</v>
+        <v>130207080</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>91759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,21 +1355,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510310</v>
+        <v>510283</v>
       </c>
       <c r="R8" t="n">
-        <v>7207347</v>
+        <v>7207343</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,23 +1462,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R9" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>91778</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,19 +1565,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>130207079</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>99284</v>
+        <v>99285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130207091</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>130207094</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>130207088</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207080</v>
+        <v>130207090</v>
       </c>
       <c r="B8" t="n">
-        <v>91759</v>
+        <v>91781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,23 +1355,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510283</v>
+        <v>510203</v>
       </c>
       <c r="R8" t="n">
-        <v>7207343</v>
+        <v>7207324</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207090</v>
+        <v>130207093</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,19 +1458,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510203</v>
+        <v>510310</v>
       </c>
       <c r="R9" t="n">
-        <v>7207324</v>
+        <v>7207347</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207093</v>
+        <v>130207080</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>91761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510310</v>
+        <v>510283</v>
       </c>
       <c r="R10" t="n">
-        <v>7207347</v>
+        <v>7207343</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
         <v>130207083</v>
       </c>
       <c r="B11" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130207081</v>
       </c>
       <c r="B12" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207079</v>
+        <v>130207089</v>
       </c>
       <c r="B13" t="n">
-        <v>91773</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510702</v>
+        <v>510144</v>
       </c>
       <c r="R13" t="n">
-        <v>7207550</v>
+        <v>7207312</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207089</v>
+        <v>130207079</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>91775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510144</v>
+        <v>510702</v>
       </c>
       <c r="R14" t="n">
-        <v>7207312</v>
+        <v>7207550</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2092,7 @@
         <v>130207097</v>
       </c>
       <c r="B15" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>130207092</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>99285</v>
+        <v>99287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -2201,50 +2201,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>99291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R16" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2286,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,45 +2308,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207082</v>
+        <v>130207092</v>
       </c>
       <c r="B17" t="n">
-        <v>99287</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510217</v>
+        <v>510260</v>
       </c>
       <c r="R17" t="n">
-        <v>7207322</v>
+        <v>7207346</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -675,50 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>915706</v>
+        <v>94152331</v>
       </c>
       <c r="B2" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2082</v>
+        <v>102108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Alfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Clangula hyemalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väg mellan Stornässundet &amp; Saxnäs, Ås lm</t>
+          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510003</v>
+        <v>508202</v>
       </c>
       <c r="R2" t="n">
-        <v>7207991</v>
+        <v>7209767</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,17 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-13</t>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Båda sidor om vägkant, nordsida mer örter och skogsrör.</t>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,27 +781,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Näslund</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94152331</v>
+        <v>130207080</v>
       </c>
       <c r="B3" t="n">
-        <v>55571</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,45 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Alfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clangula hyemalis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
+          <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508202.5377758173</v>
+        <v>510283</v>
       </c>
       <c r="R3" t="n">
-        <v>7209766.426789374</v>
+        <v>7207343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,71 +888,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123675716</v>
+        <v>130207079</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kultsjön, Ås lm</t>
+          <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509043</v>
+        <v>510702</v>
       </c>
       <c r="R4" t="n">
-        <v>7208879</v>
+        <v>7207550</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,22 +965,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,50 +1007,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130207091</v>
+        <v>130207081</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510219</v>
+        <v>510282</v>
       </c>
       <c r="R5" t="n">
-        <v>7207326</v>
+        <v>7207352</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,30 +1114,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130207094</v>
+        <v>130207083</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510310</v>
+        <v>510187</v>
       </c>
       <c r="R6" t="n">
-        <v>7207347</v>
+        <v>7207321</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,41 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130207088</v>
+        <v>915699</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>100387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2082</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Väg mellan Stornässundet &amp; Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510128</v>
+        <v>508918</v>
       </c>
       <c r="R7" t="n">
-        <v>7207308</v>
+        <v>7209120</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1302,22 +1286,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2000-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2000-08-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Norra vägkanten mot sjön, örtrikt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,53 +1311,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Peter Näslund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207090</v>
+        <v>915706</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>100387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2082</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Väg mellan Stornässundet &amp; Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510203</v>
+        <v>510003</v>
       </c>
       <c r="R8" t="n">
-        <v>7207324</v>
+        <v>7207991</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1405,22 +1388,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2000-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2000-08-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Båda sidor om vägkant, nordsida mer örter och skogsrör.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,26 +1413,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Peter Näslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207093</v>
+        <v>130207089</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1482,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510310</v>
+        <v>510144</v>
       </c>
       <c r="R9" t="n">
-        <v>7207347</v>
+        <v>7207312</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,32 +1532,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207080</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>91761</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510283</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207343</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1602,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1612,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130207083</v>
+        <v>130207078</v>
       </c>
       <c r="B11" t="n">
-        <v>91775</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,34 +1650,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510187</v>
+        <v>510693</v>
       </c>
       <c r="R11" t="n">
-        <v>7207321</v>
+        <v>7207626</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1714,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1724,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130207081</v>
+        <v>130207084</v>
       </c>
       <c r="B12" t="n">
-        <v>91775</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,34 +1762,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510282</v>
+        <v>510025</v>
       </c>
       <c r="R12" t="n">
-        <v>7207352</v>
+        <v>7207259</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,7 +1826,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1836,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207089</v>
+        <v>130207091</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,34 +1874,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510144</v>
+        <v>510219</v>
       </c>
       <c r="R13" t="n">
-        <v>7207312</v>
+        <v>7207326</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1938,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1948,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207079</v>
+        <v>130207092</v>
       </c>
       <c r="B14" t="n">
-        <v>91775</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,34 +1986,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510702</v>
+        <v>510260</v>
       </c>
       <c r="R14" t="n">
-        <v>7207550</v>
+        <v>7207346</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2060,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2090,7 @@
         <v>130207097</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130207082</v>
+        <v>123675716</v>
       </c>
       <c r="B16" t="n">
-        <v>99291</v>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,34 +2210,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510217</v>
+        <v>509043</v>
       </c>
       <c r="R16" t="n">
-        <v>7207322</v>
+        <v>7208879</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,22 +2273,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,50 +2315,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207092</v>
+        <v>130207082</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>99456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510260</v>
+        <v>510217</v>
       </c>
       <c r="R17" t="n">
-        <v>7207346</v>
+        <v>7207322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2385,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2395,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
